--- a/data/danh_sach_mon_an.xlsx
+++ b/data/danh_sach_mon_an.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BTL TRI TUE NHAN TAO\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D94A9883-C8A2-4A58-8E62-6B548FA65B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A597D6E0-5275-494D-91E2-D2EE337E25EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{83411BAF-91DA-4BCB-8993-1CE8A2F2A6CD}"/>
   </bookViews>
@@ -1025,9 +1025,6 @@
     <t>Rau đắng</t>
   </si>
   <si>
-    <t>Mắm</t>
-  </si>
-  <si>
     <t>Thịt</t>
   </si>
   <si>
@@ -1055,9 +1052,6 @@
     <t>Đắng, Ngọt</t>
   </si>
   <si>
-    <t>Béo, Mặn, Cay</t>
-  </si>
-  <si>
     <t>Béo, Mặn, Ngọt</t>
   </si>
   <si>
@@ -1077,6 +1071,12 @@
   </si>
   <si>
     <t>Củ hủ dừa xào tép nhảy là một món ăn dân dã gắn liền với vùng đất Bến Tre, nơi nổi tiếng với những rặng dừa xanh bát ngát. Đây là sự kết hợp hài hòa giữa củ hủ dừa giòn ngọt, tươi mát và tép nhảy nhỏ xíu nhưng đầy hương vị. Củ hủ dừa, phần non nhất ở lõi thân cây dừa, kết hợp cùng tép nhảy - loại tép tươi sống được bắt lên từ sông nước miền Tây - món ăn này trở thành một tuyệt phẩm không chỉ về hương vị mà còn mang đậm nét đặc trưng của ẩm thực xứ dừa. Nếu có dịp đến đây, bạn hãy  thưởng thức để cảm nhận được trọn vẹn sự tinh tế trong ẩm thực quê hương này.</t>
+  </si>
+  <si>
+    <t>Béo, Ngot</t>
+  </si>
+  <si>
+    <t>Mắm, Rau củ quả, Hải sản</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1257,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1268,7 +1268,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1303,67 +1302,6 @@
   <dxfs count="16">
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="163"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="3" tint="0.79998168889431442"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="163"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1727,31 +1665,92 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="3" tint="0.79998168889431442"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="1" xr9:uid="{DA155C87-9908-4A09-8970-82FC67BB3450}">
-      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="wholeTable" dxfId="15"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1766,19 +1765,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7BDB25AF-7EB4-41BB-8944-93EAB051A2DE}" name="Table1" displayName="Table1" ref="A1:J73" totalsRowShown="0" headerRowDxfId="0" dataDxfId="2" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7BDB25AF-7EB4-41BB-8944-93EAB051A2DE}" name="Table1" displayName="Table1" ref="A1:J73" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="A1:J73" xr:uid="{7BDB25AF-7EB4-41BB-8944-93EAB051A2DE}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{12436251-3A32-428C-AB2D-1C115EFCA7F0}" name="id" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{BB407834-412E-47FC-91C1-9887DEA79238}" name="ten" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{5A3AB2C4-3359-4F18-A8D1-6FC9F886D6D8}" name="loai" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{2CF0EE17-8EE4-4E0F-B3E1-B5FBEF7BEA24}" name="vi" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{B622A9CC-E62D-43E2-9750-1DA009468243}" name="tinh" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{6773C413-F76C-4D25-B236-2E5F9EB0678F}" name="mua" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{8A65B6F5-7B03-48B6-A694-24920FDB1069}" name="nlc" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{F62B44B8-B9FD-429A-8FF4-B26A90937990}" name="nlp" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{F9D5126C-F4E5-4A58-B38B-237B668AC4A9}" name="mo_ta" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{CB9B418A-7CD2-4E3E-8958-FDD4B1BDED47}" name="image_path" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{12436251-3A32-428C-AB2D-1C115EFCA7F0}" name="id" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{BB407834-412E-47FC-91C1-9887DEA79238}" name="ten" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{5A3AB2C4-3359-4F18-A8D1-6FC9F886D6D8}" name="loai" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{2CF0EE17-8EE4-4E0F-B3E1-B5FBEF7BEA24}" name="vi" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{B622A9CC-E62D-43E2-9750-1DA009468243}" name="tinh" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{6773C413-F76C-4D25-B236-2E5F9EB0678F}" name="mua" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{8A65B6F5-7B03-48B6-A694-24920FDB1069}" name="nlc" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{F62B44B8-B9FD-429A-8FF4-B26A90937990}" name="nlp" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{F9D5126C-F4E5-4A58-B38B-237B668AC4A9}" name="mo_ta" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{CB9B418A-7CD2-4E3E-8958-FDD4B1BDED47}" name="image_path" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2055,7 +2054,7 @@
   <dimension ref="A1:J73"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="45.625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="45.625" customWidth="1"/>
     <col min="3" max="3" width="17.3125" customWidth="1"/>
     <col min="4" max="4" width="14.1875" customWidth="1"/>
     <col min="5" max="5" width="16.5" customWidth="1"/>
@@ -2067,39 +2066,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.45">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>284</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -2126,12 +2125,12 @@
       <c r="I2" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>285</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2141,7 +2140,7 @@
         <v>144</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>24</v>
@@ -2150,7 +2149,7 @@
         <v>309</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>326</v>
@@ -2158,12 +2157,12 @@
       <c r="I3" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>279</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2173,13 +2172,13 @@
         <v>233</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>281</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>313</v>
@@ -2190,12 +2189,12 @@
       <c r="I4" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="6" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>286</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -2222,12 +2221,12 @@
       <c r="I5" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="6" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>287</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -2237,13 +2236,13 @@
         <v>105</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>313</v>
@@ -2254,12 +2253,12 @@
       <c r="I6" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="6" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>288</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -2269,7 +2268,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>281</v>
@@ -2278,7 +2277,7 @@
         <v>309</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>327</v>
@@ -2286,12 +2285,12 @@
       <c r="I7" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="6" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>289</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -2301,7 +2300,7 @@
         <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>48</v>
@@ -2318,12 +2317,12 @@
       <c r="I8" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="6" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>290</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -2333,16 +2332,16 @@
         <v>144</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>281</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>327</v>
@@ -2350,44 +2349,44 @@
       <c r="I9" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="6" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>291</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>277</v>
+        <v>339</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>313</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="6" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>292</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -2397,7 +2396,7 @@
         <v>95</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>277</v>
+        <v>339</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>48</v>
@@ -2406,7 +2405,7 @@
         <v>312</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>327</v>
@@ -2414,22 +2413,22 @@
       <c r="I11" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="6" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>276</v>
+        <v>339</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>21</v>
@@ -2446,12 +2445,12 @@
       <c r="I12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -2478,12 +2477,12 @@
       <c r="I13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -2510,12 +2509,12 @@
       <c r="I14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -2542,15 +2541,15 @@
       <c r="I15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -2574,12 +2573,12 @@
       <c r="I16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="6" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -2604,14 +2603,14 @@
         <v>276</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="J17" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -2638,12 +2637,12 @@
       <c r="I18" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J18" s="7" t="s">
+      <c r="J18" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -2670,12 +2669,12 @@
       <c r="I19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="J19" s="6" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -2702,12 +2701,12 @@
       <c r="I20" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="J20" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -2734,12 +2733,12 @@
       <c r="I21" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="J21" s="6" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>60</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -2764,14 +2763,14 @@
         <v>276</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="J22" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -2798,12 +2797,12 @@
       <c r="I23" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="J23" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -2830,12 +2829,12 @@
       <c r="I24" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J24" s="7" t="s">
+      <c r="J24" s="6" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>71</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -2862,12 +2861,12 @@
       <c r="I25" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J25" s="7" t="s">
+      <c r="J25" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -2894,12 +2893,12 @@
       <c r="I26" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="J26" s="7" t="s">
+      <c r="J26" s="6" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>80</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -2926,12 +2925,12 @@
       <c r="I27" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J27" s="7" t="s">
+      <c r="J27" s="6" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -2958,12 +2957,12 @@
       <c r="I28" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J28" s="7" t="s">
+      <c r="J28" s="6" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>89</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -2990,12 +2989,12 @@
       <c r="I29" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J29" s="7" t="s">
+      <c r="J29" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>93</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -3022,15 +3021,15 @@
       <c r="I30" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="J30" s="7" t="s">
+      <c r="J30" s="6" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="4" t="s">
         <v>100</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -3054,12 +3053,12 @@
       <c r="I31" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="J31" s="7" t="s">
+      <c r="J31" s="6" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="5" t="s">
         <v>103</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -3086,12 +3085,12 @@
       <c r="I32" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="J32" s="7" t="s">
+      <c r="J32" s="6" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="5" t="s">
         <v>108</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -3118,12 +3117,12 @@
       <c r="I33" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="J33" s="7" t="s">
+      <c r="J33" s="6" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
         <v>112</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -3150,12 +3149,12 @@
       <c r="I34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="J34" s="7" t="s">
+      <c r="J34" s="6" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="5" t="s">
         <v>116</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -3182,12 +3181,12 @@
       <c r="I35" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="J35" s="7" t="s">
+      <c r="J35" s="6" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="5" t="s">
         <v>120</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -3214,12 +3213,12 @@
       <c r="I36" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="J36" s="7" t="s">
+      <c r="J36" s="6" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -3246,12 +3245,12 @@
       <c r="I37" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J37" s="7" t="s">
+      <c r="J37" s="6" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="5" t="s">
         <v>129</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -3278,12 +3277,12 @@
       <c r="I38" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="J38" s="7" t="s">
+      <c r="J38" s="6" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="5" t="s">
         <v>133</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -3310,12 +3309,12 @@
       <c r="I39" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="J39" s="7" t="s">
+      <c r="J39" s="6" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="5" t="s">
         <v>137</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -3342,12 +3341,12 @@
       <c r="I40" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J40" s="7" t="s">
+      <c r="J40" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="5" t="s">
         <v>142</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -3374,12 +3373,12 @@
       <c r="I41" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="J41" s="7" t="s">
+      <c r="J41" s="6" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="5" t="s">
         <v>147</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -3406,12 +3405,12 @@
       <c r="I42" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="J42" s="7" t="s">
+      <c r="J42" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="5" t="s">
         <v>151</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -3438,12 +3437,12 @@
       <c r="I43" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="J43" s="7" t="s">
+      <c r="J43" s="6" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="5" t="s">
         <v>155</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -3470,12 +3469,12 @@
       <c r="I44" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="J44" s="7" t="s">
+      <c r="J44" s="6" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="5" t="s">
         <v>160</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -3502,12 +3501,12 @@
       <c r="I45" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="J45" s="7" t="s">
+      <c r="J45" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="5" t="s">
         <v>164</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -3532,14 +3531,14 @@
         <v>276</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="J46" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="J46" s="6" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="5" t="s">
         <v>167</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -3566,12 +3565,12 @@
       <c r="I47" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="J47" s="7" t="s">
+      <c r="J47" s="6" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="5" t="s">
         <v>171</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -3598,12 +3597,12 @@
       <c r="I48" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="J48" s="7" t="s">
+      <c r="J48" s="6" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="5" t="s">
         <v>175</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -3630,15 +3629,15 @@
       <c r="I49" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="J49" s="7" t="s">
+      <c r="J49" s="6" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="4" t="s">
         <v>180</v>
       </c>
       <c r="C50" s="1" t="s">
@@ -3662,12 +3661,12 @@
       <c r="I50" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="J50" s="7" t="s">
+      <c r="J50" s="6" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="5" t="s">
         <v>183</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -3694,12 +3693,12 @@
       <c r="I51" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="J51" s="7" t="s">
+      <c r="J51" s="6" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="5" t="s">
         <v>187</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -3724,12 +3723,12 @@
       <c r="I52" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="J52" s="7" t="s">
+      <c r="J52" s="6" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="5" t="s">
         <v>191</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -3756,12 +3755,12 @@
       <c r="I53" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="J53" s="7" t="s">
+      <c r="J53" s="6" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="5" t="s">
         <v>195</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -3788,12 +3787,12 @@
       <c r="I54" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="J54" s="7" t="s">
+      <c r="J54" s="6" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="5" t="s">
         <v>199</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -3820,12 +3819,12 @@
       <c r="I55" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="J55" s="7" t="s">
+      <c r="J55" s="6" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="5" t="s">
         <v>203</v>
       </c>
       <c r="B56" s="1" t="s">
@@ -3852,12 +3851,12 @@
       <c r="I56" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="J56" s="7" t="s">
+      <c r="J56" s="6" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="5" t="s">
         <v>207</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -3884,12 +3883,12 @@
       <c r="I57" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="J57" s="7" t="s">
+      <c r="J57" s="6" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="5" t="s">
         <v>211</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -3914,14 +3913,14 @@
         <v>276</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="J58" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="J58" s="6" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="5" t="s">
         <v>214</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -3948,12 +3947,12 @@
       <c r="I59" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="J59" s="7" t="s">
+      <c r="J59" s="6" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="5" t="s">
         <v>218</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -3980,12 +3979,12 @@
       <c r="I60" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="J60" s="7" t="s">
+      <c r="J60" s="6" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="5" t="s">
         <v>222</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -4012,12 +4011,12 @@
       <c r="I61" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="J61" s="7" t="s">
+      <c r="J61" s="6" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="5" t="s">
         <v>227</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -4044,12 +4043,12 @@
       <c r="I62" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="J62" s="7" t="s">
+      <c r="J62" s="6" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="5" t="s">
         <v>231</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -4076,12 +4075,12 @@
       <c r="I63" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J63" s="7" t="s">
+      <c r="J63" s="6" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="5" t="s">
         <v>236</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -4108,12 +4107,12 @@
       <c r="I64" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="J64" s="7" t="s">
+      <c r="J64" s="6" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="5" t="s">
         <v>240</v>
       </c>
       <c r="B65" s="1" t="s">
@@ -4140,12 +4139,12 @@
       <c r="I65" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="J65" s="7" t="s">
+      <c r="J65" s="6" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="5" t="s">
         <v>244</v>
       </c>
       <c r="B66" s="1" t="s">
@@ -4172,12 +4171,12 @@
       <c r="I66" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="J66" s="7" t="s">
+      <c r="J66" s="6" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="5" t="s">
         <v>248</v>
       </c>
       <c r="B67" s="1" t="s">
@@ -4204,12 +4203,12 @@
       <c r="I67" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="J67" s="7" t="s">
+      <c r="J67" s="6" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="5" t="s">
         <v>252</v>
       </c>
       <c r="B68" s="1" t="s">
@@ -4236,12 +4235,12 @@
       <c r="I68" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="J68" s="7" t="s">
+      <c r="J68" s="6" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="5" t="s">
         <v>256</v>
       </c>
       <c r="B69" s="1" t="s">
@@ -4268,12 +4267,12 @@
       <c r="I69" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="J69" s="7" t="s">
+      <c r="J69" s="6" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="5" t="s">
         <v>260</v>
       </c>
       <c r="B70" s="1" t="s">
@@ -4300,12 +4299,12 @@
       <c r="I70" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="J70" s="7" t="s">
+      <c r="J70" s="6" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="5" t="s">
         <v>264</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -4328,12 +4327,12 @@
       <c r="I71" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="J71" s="7" t="s">
+      <c r="J71" s="6" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="5" t="s">
         <v>268</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -4360,50 +4359,42 @@
       <c r="I72" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="J72" s="7" t="s">
+      <c r="J72" s="6" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="C73" s="9" t="s">
+      <c r="C73" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D73" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="E73" s="9" t="s">
+      <c r="D73" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E73" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="I73" s="9" t="s">
+      <c r="F73" s="8"/>
+      <c r="G73" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="I73" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="J73" s="10" t="s">
+      <c r="J73" s="9" t="s">
         <v>275</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J73">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="3" tint="0.79998168889431442"/>
-        <color theme="7" tint="0.79998168889431442"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -4415,6 +4406,14 @@
           <x14:id>{8519CB71-57B9-4E7A-8D1E-7D486387261A}</x14:id>
         </ext>
       </extLst>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="3" tint="0.79998168889431442"/>
+        <color theme="7" tint="0.79998168889431442"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/danh_sach_mon_an.xlsx
+++ b/data/danh_sach_mon_an.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BTL TRI TUE NHAN TAO\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A597D6E0-5275-494D-91E2-D2EE337E25EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834E3BF4-7A12-4E6E-A4F0-DA05D7B44753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{83411BAF-91DA-4BCB-8993-1CE8A2F2A6CD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="346">
   <si>
     <t>id</t>
   </si>
@@ -1014,9 +1014,6 @@
   </si>
   <si>
     <t xml:space="preserve">Mực trứng nhồi nhum biển sốt mè gạo lứt </t>
-  </si>
-  <si>
-    <t>Chao</t>
   </si>
   <si>
     <t>Rau củ quả</t>
@@ -2140,7 +2137,7 @@
         <v>144</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>24</v>
@@ -2149,7 +2146,7 @@
         <v>309</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>326</v>
@@ -2172,19 +2169,19 @@
         <v>233</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>281</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>313</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>282</v>
@@ -2216,7 +2213,7 @@
         <v>313</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>314</v>
@@ -2236,19 +2233,19 @@
         <v>105</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>313</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>316</v>
@@ -2268,7 +2265,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>281</v>
@@ -2277,10 +2274,10 @@
         <v>309</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>318</v>
@@ -2300,7 +2297,7 @@
         <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>48</v>
@@ -2312,7 +2309,7 @@
         <v>313</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>320</v>
@@ -2332,19 +2329,19 @@
         <v>144</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>281</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>322</v>
@@ -2358,25 +2355,25 @@
         <v>291</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>313</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>323</v>
@@ -2396,7 +2393,7 @@
         <v>95</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>48</v>
@@ -2405,10 +2402,10 @@
         <v>312</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>324</v>
@@ -2428,7 +2425,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>21</v>
@@ -2603,7 +2600,7 @@
         <v>276</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>39</v>
@@ -2763,7 +2760,7 @@
         <v>276</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>62</v>
@@ -3531,7 +3528,7 @@
         <v>276</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>166</v>
@@ -3913,7 +3910,7 @@
         <v>276</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J58" s="6" t="s">
         <v>213</v>

--- a/data/danh_sach_mon_an.xlsx
+++ b/data/danh_sach_mon_an.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BTL TRI TUE NHAN TAO\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834E3BF4-7A12-4E6E-A4F0-DA05D7B44753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0423CEB-44E3-4A4F-812E-B2F8FAE9CC70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{83411BAF-91DA-4BCB-8993-1CE8A2F2A6CD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="356">
   <si>
     <t>id</t>
   </si>
@@ -974,12 +974,6 @@
     <t>Gỏi xoài cá sặc</t>
   </si>
   <si>
-    <t>Mùa khô, Mùa mưa</t>
-  </si>
-  <si>
-    <t>Cá</t>
-  </si>
-  <si>
     <t>Gỏi xoài cá sặc, món dân dã miền Nam, nổi bật với hương vị hài hòa, khó cưỡng. Món ăn lý tưởng cho ngày hè nóng nhờ xoài xanh chua giòn và cá sặc khô đậm đà. Nguyên liệu gồm xoài thái sợi, cá nướng thơm, cùng nước mắm tỏi ớt, đường, chanh, rau thơm hòa quyện. Vị chua nhẹ của xoài, mặn béo của cá khô thêm chút cay nơi đầu lưỡi tạo cảm giác khó quên. Đây là món khai vị hấp dẫn và đem lại nét mới mẻ cho bữa cơm gia đình.</t>
   </si>
   <si>
@@ -1025,33 +1019,12 @@
     <t>Thịt</t>
   </si>
   <si>
-    <t>Bột</t>
-  </si>
-  <si>
-    <t>Bánh tằm</t>
-  </si>
-  <si>
-    <t>Hải sản</t>
-  </si>
-  <si>
-    <t>Mùa mưa, Mùa khô</t>
-  </si>
-  <si>
     <t>Quanh năm</t>
   </si>
   <si>
-    <t>Ngọt, Cay, Mặn</t>
-  </si>
-  <si>
-    <t>Chua, Cay, Mặn</t>
-  </si>
-  <si>
     <t>Đắng, Ngọt</t>
   </si>
   <si>
-    <t>Béo, Mặn, Ngọt</t>
-  </si>
-  <si>
     <t>Mặn, Ngọt</t>
   </si>
   <si>
@@ -1073,7 +1046,64 @@
     <t>Béo, Ngot</t>
   </si>
   <si>
-    <t>Mắm, Rau củ quả, Hải sản</t>
+    <t>Chua, Ngọt, Đắng</t>
+  </si>
+  <si>
+    <t>Chua, Cay</t>
+  </si>
+  <si>
+    <t>Mùa mưa</t>
+  </si>
+  <si>
+    <t>Lá giang</t>
+  </si>
+  <si>
+    <t>Cá, Trái cây</t>
+  </si>
+  <si>
+    <t>Mùa khô, Mùa nước nổi</t>
+  </si>
+  <si>
+    <t>Chua, Ngọt, Mặn</t>
+  </si>
+  <si>
+    <t>Cá, Gạo</t>
+  </si>
+  <si>
+    <t>Bột, Trứng</t>
+  </si>
+  <si>
+    <t>Béo, Ngọt</t>
+  </si>
+  <si>
+    <t>Mùa khô</t>
+  </si>
+  <si>
+    <t>Nước cốt dừa</t>
+  </si>
+  <si>
+    <t>Bánh tằm, Thịt</t>
+  </si>
+  <si>
+    <t>Béo</t>
+  </si>
+  <si>
+    <t>Cá, Hải sản, Bún</t>
+  </si>
+  <si>
+    <t>Mắm</t>
+  </si>
+  <si>
+    <t>Hải sản, Gạo</t>
+  </si>
+  <si>
+    <t>Rau củ quả, Dầu mè</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ngọt</t>
+  </si>
+  <si>
+    <t>Gạo, Thịt, Trứng</t>
   </si>
 </sst>
 </file>
@@ -2105,7 +2135,7 @@
         <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>294</v>
+        <v>336</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>38</v>
@@ -2137,7 +2167,7 @@
         <v>144</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>24</v>
@@ -2146,10 +2176,10 @@
         <v>309</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>310</v>
@@ -2169,19 +2199,19 @@
         <v>233</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>335</v>
+        <v>294</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>281</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>282</v>
@@ -2201,22 +2231,22 @@
         <v>82</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>294</v>
+        <v>342</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>301</v>
@@ -2227,28 +2257,28 @@
         <v>287</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>105</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>302</v>
@@ -2259,13 +2289,13 @@
         <v>288</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>281</v>
@@ -2274,13 +2304,13 @@
         <v>309</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>303</v>
@@ -2291,28 +2321,28 @@
         <v>289</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>304</v>
@@ -2323,28 +2353,28 @@
         <v>290</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>144</v>
+        <v>16</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>281</v>
+        <v>33</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>305</v>
@@ -2355,28 +2385,28 @@
         <v>291</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>313</v>
+        <v>350</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>306</v>
@@ -2387,28 +2417,28 @@
         <v>292</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>95</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>307</v>
@@ -2425,19 +2455,19 @@
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>276</v>
+        <v>346</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>276</v>
+        <v>355</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>276</v>
+        <v>324</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>12</v>
@@ -2600,7 +2630,7 @@
         <v>276</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>39</v>
@@ -2760,7 +2790,7 @@
         <v>276</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>62</v>
@@ -3528,7 +3558,7 @@
         <v>276</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>166</v>
@@ -3910,7 +3940,7 @@
         <v>276</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="J58" s="6" t="s">
         <v>213</v>

--- a/data/danh_sach_mon_an.xlsx
+++ b/data/danh_sach_mon_an.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BTL TRI TUE NHAN TAO\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0423CEB-44E3-4A4F-812E-B2F8FAE9CC70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE9B11AD-466B-4ED8-9A25-B994953FF40E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{83411BAF-91DA-4BCB-8993-1CE8A2F2A6CD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="409">
   <si>
     <t>id</t>
   </si>
@@ -869,9 +869,6 @@
     <t>.</t>
   </si>
   <si>
-    <t>..</t>
-  </si>
-  <si>
     <t>mua</t>
   </si>
   <si>
@@ -1104,6 +1101,168 @@
   </si>
   <si>
     <t>Gạo, Thịt, Trứng</t>
+  </si>
+  <si>
+    <t>Mùa tết</t>
+  </si>
+  <si>
+    <t>Nếp</t>
+  </si>
+  <si>
+    <t>Rau củ quả, Nước cốt dừa</t>
+  </si>
+  <si>
+    <t>Hủ tiếu, Thịt, Hải sản</t>
+  </si>
+  <si>
+    <t>Béo, Mặn</t>
+  </si>
+  <si>
+    <t>Rau củ quả, Chao</t>
+  </si>
+  <si>
+    <t>Lá chúc</t>
+  </si>
+  <si>
+    <t>Ngọt, Béo</t>
+  </si>
+  <si>
+    <t>Hải sản</t>
+  </si>
+  <si>
+    <t>Bún, Hải sản</t>
+  </si>
+  <si>
+    <t>Nước cốt dừa, Rau củ quả</t>
+  </si>
+  <si>
+    <t>Cay</t>
+  </si>
+  <si>
+    <t>Bún, Thịt</t>
+  </si>
+  <si>
+    <t>Bột</t>
+  </si>
+  <si>
+    <t>Cay, Mặn</t>
+  </si>
+  <si>
+    <t>Cá</t>
+  </si>
+  <si>
+    <t>Ngọt, Mặn</t>
+  </si>
+  <si>
+    <t>Bún, Cá</t>
+  </si>
+  <si>
+    <t>Mắm, Rau củ quả</t>
+  </si>
+  <si>
+    <t>Thịt, Hải sản</t>
+  </si>
+  <si>
+    <t>Sen</t>
+  </si>
+  <si>
+    <t>Bột, Gạo</t>
+  </si>
+  <si>
+    <t>Bún, Cá, Thịt</t>
+  </si>
+  <si>
+    <t>Gạo, Thịt</t>
+  </si>
+  <si>
+    <t>Gạo, Hải sản, Trứng</t>
+  </si>
+  <si>
+    <t>Bột, Thịt, Hải sản</t>
+  </si>
+  <si>
+    <t>Mùa trái cây</t>
+  </si>
+  <si>
+    <t>Bột, Thịt</t>
+  </si>
+  <si>
+    <t>Gạo, Cá, Trứng</t>
+  </si>
+  <si>
+    <t>Cay, Mặn, Béo</t>
+  </si>
+  <si>
+    <t>Ngọt</t>
+  </si>
+  <si>
+    <t>Chua, Mặn</t>
+  </si>
+  <si>
+    <t>Ngọt, Cay</t>
+  </si>
+  <si>
+    <t>Thị, Hải sản</t>
+  </si>
+  <si>
+    <t>Chua, Ngọt, Béo</t>
+  </si>
+  <si>
+    <t>Béo, Ngọt, Cay</t>
+  </si>
+  <si>
+    <t>Côn trùng</t>
+  </si>
+  <si>
+    <t>Gạo</t>
+  </si>
+  <si>
+    <t>Dầu mè</t>
+  </si>
+  <si>
+    <t>Thịt, Bún</t>
+  </si>
+  <si>
+    <t>Béo, Ngọt, Mặn</t>
+  </si>
+  <si>
+    <t>Thịt, Hải sản, Trứng</t>
+  </si>
+  <si>
+    <t>Béo, Chua, Cay</t>
+  </si>
+  <si>
+    <t>Béo, Mặn, Ngọt</t>
+  </si>
+  <si>
+    <t>Trái cây, Nếp</t>
+  </si>
+  <si>
+    <t>Mặn, Cay</t>
+  </si>
+  <si>
+    <t>Ngọt, Đắng</t>
+  </si>
+  <si>
+    <t>Mặn, Béo</t>
+  </si>
+  <si>
+    <t>Hải sản, Bột</t>
+  </si>
+  <si>
+    <t>Mặn, Ngọt, Béo</t>
+  </si>
+  <si>
+    <t>Ngọt, Mặn, Béo</t>
+  </si>
+  <si>
+    <t>Thịt, Hải sản, Cá</t>
+  </si>
+  <si>
+    <t>Mặn, Ngot</t>
+  </si>
+  <si>
+    <t>Mùa khô, Mùa mưa</t>
   </si>
 </sst>
 </file>
@@ -2109,7 +2268,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>5</v>
@@ -2126,322 +2285,322 @@
     </row>
     <row r="2" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
       <c r="A2" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="6" t="s">
         <v>298</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
       <c r="A3" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>144</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="J3" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
       <c r="A4" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>233</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="6" t="s">
         <v>282</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
       <c r="A5" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
       <c r="A6" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>105</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
       <c r="A7" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
       <c r="A8" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="I8" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
       <c r="A9" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
       <c r="A10" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G10" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>351</v>
-      </c>
       <c r="I10" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
       <c r="A11" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>95</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G11" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="I11" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
@@ -2455,19 +2614,19 @@
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>12</v>
@@ -2487,19 +2646,19 @@
         <v>16</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>276</v>
+        <v>344</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>276</v>
+        <v>355</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>276</v>
+        <v>356</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>276</v>
+        <v>357</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>17</v>
@@ -2519,19 +2678,19 @@
         <v>23</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>277</v>
+        <v>328</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>276</v>
+        <v>358</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>25</v>
@@ -2551,19 +2710,19 @@
         <v>23</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>276</v>
+        <v>358</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>29</v>
@@ -2583,19 +2742,19 @@
         <v>23</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>276</v>
+        <v>359</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>277</v>
+        <v>325</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>277</v>
+        <v>360</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>37</v>
@@ -2615,22 +2774,22 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>277</v>
+        <v>328</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>276</v>
+        <v>325</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>276</v>
+        <v>361</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>39</v>
@@ -2647,19 +2806,19 @@
         <v>42</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>276</v>
+        <v>362</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>276</v>
+        <v>363</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>276</v>
+        <v>346</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>44</v>
@@ -2679,19 +2838,19 @@
         <v>23</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>276</v>
+        <v>364</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>49</v>
@@ -2711,19 +2870,19 @@
         <v>16</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>277</v>
+        <v>344</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>276</v>
+        <v>355</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>277</v>
+        <v>356</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>277</v>
+        <v>365</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>53</v>
@@ -2743,19 +2902,19 @@
         <v>23</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>276</v>
+        <v>366</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>57</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>276</v>
+        <v>367</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>58</v>
@@ -2775,22 +2934,22 @@
         <v>42</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>276</v>
+        <v>345</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>276</v>
+        <v>363</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>62</v>
@@ -2807,19 +2966,19 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>276</v>
+        <v>348</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>276</v>
+        <v>368</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>277</v>
+        <v>346</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>65</v>
@@ -2839,19 +2998,19 @@
         <v>11</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>276</v>
+        <v>369</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>276</v>
+        <v>345</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>277</v>
+        <v>363</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>69</v>
@@ -2871,19 +3030,19 @@
         <v>23</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>276</v>
+        <v>370</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>74</v>
@@ -2903,19 +3062,19 @@
         <v>23</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>277</v>
+        <v>371</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>276</v>
+        <v>372</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>277</v>
+        <v>373</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>78</v>
@@ -2935,19 +3094,19 @@
         <v>82</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>276</v>
+        <v>341</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>276</v>
+        <v>374</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>276</v>
+        <v>375</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>83</v>
@@ -2967,19 +3126,19 @@
         <v>16</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>276</v>
+        <v>362</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>277</v>
+        <v>326</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>277</v>
+        <v>376</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>276</v>
+        <v>346</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>87</v>
@@ -2999,19 +3158,19 @@
         <v>23</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>276</v>
+        <v>371</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>276</v>
+        <v>377</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>276</v>
+        <v>350</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>91</v>
@@ -3031,19 +3190,19 @@
         <v>95</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>276</v>
+        <v>371</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>96</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>276</v>
+        <v>363</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>97</v>
@@ -3063,19 +3222,19 @@
         <v>23</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>276</v>
+        <v>344</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>276</v>
+        <v>378</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>277</v>
+        <v>346</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>101</v>
@@ -3095,19 +3254,19 @@
         <v>105</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>277</v>
+        <v>344</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>276</v>
+        <v>379</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>106</v>
@@ -3127,19 +3286,19 @@
         <v>23</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>276</v>
+        <v>371</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>276</v>
+        <v>364</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>276</v>
+        <v>350</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>110</v>
@@ -3159,19 +3318,19 @@
         <v>16</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>276</v>
+        <v>344</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>276</v>
+        <v>380</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>114</v>
@@ -3191,19 +3350,19 @@
         <v>16</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>276</v>
+        <v>362</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>276</v>
+        <v>122</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>277</v>
+        <v>346</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>118</v>
@@ -3223,16 +3382,16 @@
         <v>122</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>276</v>
+        <v>362</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>276</v>
+        <v>355</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>276</v>
+        <v>122</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>276</v>
@@ -3255,16 +3414,16 @@
         <v>122</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>276</v>
+        <v>362</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>277</v>
+        <v>122</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>276</v>
@@ -3287,19 +3446,19 @@
         <v>23</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>276</v>
+        <v>382</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>131</v>
@@ -3319,19 +3478,19 @@
         <v>23</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>277</v>
+        <v>371</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>276</v>
+        <v>383</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>276</v>
+        <v>350</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>135</v>
@@ -3351,19 +3510,19 @@
         <v>139</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>276</v>
+        <v>384</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>276</v>
+        <v>345</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>276</v>
+        <v>370</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>277</v>
+        <v>323</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>140</v>
@@ -3383,19 +3542,19 @@
         <v>95</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>276</v>
+        <v>355</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>276</v>
+        <v>325</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>145</v>
@@ -3415,16 +3574,16 @@
         <v>122</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>276</v>
+        <v>385</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>276</v>
+        <v>355</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>276</v>
+        <v>122</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>276</v>
@@ -3447,19 +3606,19 @@
         <v>144</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>276</v>
+        <v>386</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>276</v>
+        <v>325</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>153</v>
@@ -3479,19 +3638,19 @@
         <v>95</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>276</v>
+        <v>387</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>157</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>276</v>
+        <v>388</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>158</v>
@@ -3511,19 +3670,19 @@
         <v>23</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>277</v>
+        <v>389</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>157</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>276</v>
+        <v>370</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>277</v>
+        <v>323</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>162</v>
@@ -3543,22 +3702,22 @@
         <v>139</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>276</v>
+        <v>390</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>157</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>277</v>
+        <v>391</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>166</v>
@@ -3575,19 +3734,19 @@
         <v>16</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>157</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>276</v>
+        <v>392</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>276</v>
+        <v>393</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>169</v>
@@ -3607,16 +3766,16 @@
         <v>122</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>276</v>
+        <v>385</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>57</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>276</v>
+        <v>122</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>276</v>
@@ -3639,19 +3798,19 @@
         <v>144</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>57</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>277</v>
+        <v>326</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>276</v>
+        <v>394</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>177</v>
@@ -3671,19 +3830,19 @@
         <v>16</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>57</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>276</v>
+        <v>380</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>181</v>
@@ -3703,19 +3862,19 @@
         <v>139</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>277</v>
+        <v>395</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>96</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>276</v>
+        <v>345</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>276</v>
+        <v>396</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>185</v>
@@ -3734,18 +3893,20 @@
       <c r="C52" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D52" s="1"/>
+      <c r="D52" s="1" t="s">
+        <v>397</v>
+      </c>
       <c r="E52" s="1" t="s">
         <v>96</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>276</v>
+        <v>391</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>277</v>
+        <v>323</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>189</v>
@@ -3765,19 +3926,19 @@
         <v>42</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>276</v>
+        <v>348</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>96</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>276</v>
+        <v>370</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>276</v>
+        <v>365</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>193</v>
@@ -3797,19 +3958,19 @@
         <v>144</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>276</v>
+        <v>398</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>96</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>276</v>
+        <v>363</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>197</v>
@@ -3829,19 +3990,19 @@
         <v>144</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>276</v>
+        <v>362</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>276</v>
+        <v>378</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>276</v>
+        <v>346</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>201</v>
@@ -3861,19 +4022,19 @@
         <v>144</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>276</v>
+        <v>362</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>277</v>
+        <v>355</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>276</v>
+        <v>399</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>276</v>
+        <v>346</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>205</v>
@@ -3893,16 +4054,16 @@
         <v>122</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>276</v>
+        <v>122</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>276</v>
@@ -3925,22 +4086,22 @@
         <v>11</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>276</v>
+        <v>384</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>276</v>
+        <v>370</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J58" s="6" t="s">
         <v>213</v>
@@ -3957,19 +4118,19 @@
         <v>144</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>276</v>
+        <v>400</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>276</v>
+        <v>325</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>216</v>
@@ -3989,19 +4150,19 @@
         <v>144</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>276</v>
+        <v>354</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>220</v>
@@ -4021,19 +4182,19 @@
         <v>144</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>276</v>
+        <v>401</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>224</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>276</v>
+        <v>382</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>225</v>
@@ -4053,19 +4214,19 @@
         <v>105</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>224</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>276</v>
+        <v>378</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>229</v>
@@ -4085,19 +4246,19 @@
         <v>233</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>224</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>276</v>
+        <v>345</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>276</v>
+        <v>370</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>234</v>
@@ -4117,16 +4278,16 @@
         <v>122</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>224</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>276</v>
+        <v>122</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>276</v>
@@ -4149,19 +4310,19 @@
         <v>144</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>224</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>276</v>
+        <v>370</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>242</v>
@@ -4181,19 +4342,19 @@
         <v>144</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>277</v>
+        <v>402</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>276</v>
+        <v>345</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>276</v>
+        <v>363</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>277</v>
+        <v>323</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>246</v>
@@ -4213,19 +4374,19 @@
         <v>23</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>276</v>
+        <v>404</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>276</v>
+        <v>345</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>276</v>
+        <v>403</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>250</v>
@@ -4245,19 +4406,19 @@
         <v>23</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>276</v>
+        <v>385</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>276</v>
+        <v>372</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>254</v>
@@ -4277,19 +4438,19 @@
         <v>82</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>276</v>
+        <v>335</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>276</v>
+        <v>345</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>276</v>
+        <v>374</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>258</v>
@@ -4309,19 +4470,19 @@
         <v>233</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>276</v>
+        <v>341</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>276</v>
+        <v>345</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>276</v>
+        <v>370</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>262</v>
@@ -4340,16 +4501,20 @@
       <c r="C71" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D71" s="1"/>
+      <c r="D71" s="1" t="s">
+        <v>405</v>
+      </c>
       <c r="E71" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="G71" s="1"/>
+        <v>308</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>325</v>
+      </c>
       <c r="H71" s="1" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>266</v>
@@ -4369,19 +4534,19 @@
         <v>233</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>277</v>
+        <v>406</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>276</v>
+        <v>350</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>270</v>
@@ -4401,17 +4566,19 @@
         <v>11</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>276</v>
+        <v>407</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F73" s="8"/>
+      <c r="F73" s="8" t="s">
+        <v>408</v>
+      </c>
       <c r="G73" s="8" t="s">
-        <v>276</v>
+        <v>370</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="I73" s="8" t="s">
         <v>274</v>
